--- a/politicas.xlsx
+++ b/politicas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IA\Dropbox\Claude_IA\Simulador_Credi&amp;Gente\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio.schmid\Dropbox\Claude_IA\Simulador_Credi&amp;Gente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F13D0D7C-4B3A-485A-B6BB-BFD731ED4F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBEF817-DB12-49E4-94D2-448335C57F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DFE5EDE-F4D3-490E-9781-EFB6B5595884}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DFE5EDE-F4D3-490E-9781-EFB6B5595884}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -489,18 +489,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC3E43F-95FB-47CD-84FE-CE45DC68210E}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.36328125" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
-    <col min="4" max="4" width="14.6328125" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="19.453125" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -538,7 +538,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -553,7 +553,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -576,7 +576,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -599,7 +599,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -607,14 +607,14 @@
         <v>2</v>
       </c>
       <c r="C6" s="4">
-        <v>7.0000000000000007E-2</v>
+        <v>0.15</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -622,14 +622,14 @@
         <v>5</v>
       </c>
       <c r="C7" s="4">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -637,20 +637,22 @@
         <v>6</v>
       </c>
       <c r="C8" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="4">
         <v>0.2</v>
       </c>
-      <c r="D8" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>0.1</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" s="4">
         <v>0.05</v>
       </c>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -658,19 +660,19 @@
         <v>12</v>
       </c>
       <c r="C9" s="4">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="D9" s="4">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="4">
         <v>0.2</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.1</v>
       </c>
     </row>
   </sheetData>
